--- a/output/pdf_financials_xlsx/NRDX.xlsx
+++ b/output/pdf_financials_xlsx/NRDX.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>11.140175</v>
+        <v>-11.140175</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>2.666657</v>
+        <v>-2.666657</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>11.140175</v>
+        <v>-11.140175</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>2.666657</v>
+        <v>-2.666657</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>11.140175</v>
+        <v>-11.140175</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>2.666657</v>
+        <v>-2.666657</v>
       </c>
     </row>
     <row r="24">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>11.140175</v>
+        <v>-11.140175</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>2.666657</v>
+        <v>-2.666657</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>11.156141</v>
+        <v>-11.124209</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2.265477</v>
+        <v>-2.134693</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>2.732049</v>
+        <v>-2.601265</v>
       </c>
     </row>
     <row r="30">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1934,13 +1934,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>6.967835</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>7.207467</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>7.242735</v>
       </c>
     </row>
     <row r="93">
@@ -3187,7 +3187,11 @@
           <t>Reserves 13,15</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -3404,7 +3408,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
         <v>6.967835</v>
       </c>
@@ -5108,10 +5116,10 @@
         </is>
       </c>
       <c r="F80" s="5" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="G80" s="5" t="n">
-        <v>2.666657</v>
+        <v>-2.666657</v>
       </c>
     </row>
     <row r="81">
@@ -5190,13 +5198,13 @@
         </is>
       </c>
       <c r="E83" s="5" t="n">
-        <v>11.129212</v>
+        <v>-11.129212</v>
       </c>
       <c r="F83" s="5" t="n">
-        <v>2.073469</v>
+        <v>-2.073469</v>
       </c>
       <c r="G83" s="5" t="n">
-        <v>2.086482</v>
+        <v>-2.086482</v>
       </c>
     </row>
     <row r="84">
@@ -5696,10 +5704,10 @@
         </is>
       </c>
       <c r="E99" s="5" t="n">
-        <v>11.140175</v>
+        <v>-11.140175</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -5793,10 +5801,10 @@
         </is>
       </c>
       <c r="E102" s="5" t="n">
-        <v>11.140175</v>
+        <v>-11.140175</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>2.200085</v>
+        <v>-2.200085</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -5892,10 +5900,10 @@
         </is>
       </c>
       <c r="E105" s="5" t="n">
-        <v>11.129212</v>
+        <v>-11.129212</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>2.073469</v>
+        <v>-2.073469</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NRDX.xlsx
+++ b/output/pdf_financials_xlsx/NRDX.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.06357599999999999</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.115505</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.017952</v>
       </c>
     </row>
     <row r="13">
@@ -879,13 +879,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-11.140175</v>
+        <v>-11.076599</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-2.200085</v>
+        <v>-2.08458</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.666657</v>
+        <v>-2.648705</v>
       </c>
     </row>
     <row r="28">
@@ -911,13 +911,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-11.124209</v>
+        <v>-11.060633</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-2.134693</v>
+        <v>-2.019188</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.601265</v>
+        <v>-2.583313</v>
       </c>
     </row>
     <row r="30">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E97" s="5" t="n">
@@ -5665,7 +5665,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">

--- a/output/pdf_financials_xlsx/NRDX.xlsx
+++ b/output/pdf_financials_xlsx/NRDX.xlsx
@@ -529,13 +529,13 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.583449</v>
+        <v>0.662723</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.903111</v>
+        <v>1.021274</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.302521</v>
+        <v>0.434575</v>
       </c>
     </row>
     <row r="8">
@@ -577,13 +577,13 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.583449</v>
+        <v>0.662723</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.903111</v>
+        <v>1.021274</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.302521</v>
+        <v>0.434575</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.190749</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.086448</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.082124</v>
       </c>
     </row>
     <row r="68">
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.216528</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
@@ -2603,7 +2603,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.216528</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-1.962648</v>
+        <v>-2.179176</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-2.110848</v>
@@ -4032,7 +4032,11 @@
           <t>Proceeds from private placement</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr"/>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E45" s="5" t="n">
         <v>7</v>
       </c>
@@ -4458,7 +4462,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
         <v>-0.216528</v>
       </c>
@@ -4861,7 +4869,11 @@
           <t>Public company costs and director fees 15</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
         <v>0.079274</v>
       </c>
